--- a/各省历史油价数据.xlsx
+++ b/各省历史油价数据.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\31007384\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\31007384\Desktop\新建文件夹\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762DA667-03CE-48DB-BED9-9F8A99BE351A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC68849-5D77-45AA-B339-361BF9C98E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="43" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="48" activeTab="53" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="广东省" sheetId="1" r:id="rId1"/>
@@ -203,9 +203,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>调价日期</t>
-  </si>
-  <si>
     <t>89汽油</t>
   </si>
   <si>
@@ -220,12 +217,16 @@
   <si>
     <t>0柴油</t>
   </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +278,13 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -306,7 +314,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -332,6 +340,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21864,23 +21875,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -22255,23 +22266,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -22646,23 +22657,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -23748,23 +23759,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -24130,6 +24141,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24850,23 +24862,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -25241,23 +25253,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -25632,23 +25644,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -26023,23 +26035,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -26414,23 +26426,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -26805,23 +26817,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -27197,23 +27209,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -27588,23 +27600,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -28690,23 +28702,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -29081,23 +29093,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -29472,23 +29484,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -29863,23 +29875,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -30254,23 +30266,23 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
